--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486371_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486371_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1213</v>
+        <v>5.7956</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9165</v>
+        <v>4.2518</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2048</v>
+        <v>1.5439</v>
       </c>
       <c r="G2" t="n">
         <v>5.0513</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7125</v>
+        <v>-0.0382</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U2" t="n">
-        <v>0.041</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2468</v>
+        <v>3.8743</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1985</v>
+        <v>1.7392</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0482</v>
+        <v>2.1351</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8662</v>
+        <v>-0.1351</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3587</v>
+        <v>1.3232</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5076000000000001</v>
+        <v>-1.4582</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6179</v>
+        <v>0.4061</v>
       </c>
       <c r="K3" t="n">
-        <v>1.241</v>
+        <v>0.995</v>
       </c>
       <c r="L3" t="n">
-        <v>1.377</v>
+        <v>-0.5888</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7517</v>
+        <v>-0.5412</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8823</v>
+        <v>0.3282</v>
       </c>
       <c r="O3" t="n">
         <v>-0.8694</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3806</v>
+        <v>0.8349</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1032</v>
+        <v>0.2031</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2774</v>
+        <v>0.6318</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.8695</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8031</v>
+        <v>3.4915</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0687</v>
+        <v>2.7515</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7344</v>
+        <v>0.74</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1351</v>
+        <v>0.8662</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3232</v>
+        <v>0.3587</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4582</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4061</v>
+        <v>2.6179</v>
       </c>
       <c r="K4" t="n">
-        <v>0.995</v>
+        <v>1.241</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5888</v>
+        <v>1.377</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5412</v>
+        <v>-1.7517</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3282</v>
+        <v>-0.8823</v>
       </c>
       <c r="O4" t="n">
         <v>-0.8694</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2364</v>
+        <v>1.6253</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4675</v>
+        <v>0.6561</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2311</v>
+        <v>0.9692</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8695</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1823</v>
+        <v>2.4868</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1572</v>
+        <v>1.4924</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0251</v>
+        <v>0.9943</v>
       </c>
       <c r="G5" t="n">
         <v>2.2116</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0359</v>
+        <v>0.3404</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4349</v>
+        <v>0.4041</v>
       </c>
       <c r="V5" t="n">
         <v>0.3698</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4653</v>
+        <v>1.7072</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004</v>
+        <v>0.1843</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4613</v>
+        <v>1.5229</v>
       </c>
       <c r="G6" t="n">
         <v>0.0888</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6234</v>
+        <v>-0.3815</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.822</v>
+        <v>-0.6417</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1985</v>
+        <v>0.2602</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6474</v>
+        <v>0.709</v>
       </c>
       <c r="E7" t="n">
         <v>0.6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0474</v>
+        <v>0.1091</v>
       </c>
       <c r="G7" t="n">
         <v>0.08749999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0274</v>
+        <v>0.0342</v>
       </c>
       <c r="T7" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V7" t="n">
         <v>0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2835</v>
+        <v>-0.3338</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7944</v>
+        <v>-0.9494</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0779</v>
+        <v>0.6155</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4418</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5328</v>
+        <v>0.9154</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3581</v>
+        <v>0.2031</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1746</v>
+        <v>0.7123</v>
       </c>
       <c r="V8" t="n">
         <v>2.4552</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5077</v>
+        <v>-0.4358</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5782</v>
+        <v>-0.6583</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.2225</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2221</v>
+        <v>-1.7056</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9002</v>
+        <v>-1.4753</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6781</v>
+        <v>-0.2303</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7633</v>
+        <v>-0.7053</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.0365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1912</v>
+        <v>-0.7418</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5412</v>
+        <v>-1.0003</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3282</v>
+        <v>-1.5118</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8694</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.8276</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>1.728</v>
+        <v>-0.3827</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7487</v>
+        <v>-0.5179</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9794</v>
+        <v>0.1352</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3698</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.036</v>
+        <v>-1.418</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9503</v>
+        <v>-1.1803</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0858</v>
+        <v>-0.2377</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7056</v>
+        <v>0.2221</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4753</v>
+        <v>0.9002</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2303</v>
+        <v>-0.6781</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7053</v>
+        <v>0.7633</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0365</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7418</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0003</v>
+        <v>-0.5412</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5118</v>
+        <v>0.3282</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.8694</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.983</v>
+        <v>0.8178</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8099</v>
+        <v>0.1466</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.173</v>
+        <v>0.6711</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3698</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.2599</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.273</v>
+        <v>-1.4589</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3482</v>
+        <v>-2.5032</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0751</v>
+        <v>1.0443</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1655</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8495</v>
+        <v>0.6636</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0721</v>
+        <v>-0.0829</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7774</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.3904</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9662</v>
+        <v>-2.1087</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3304</v>
+        <v>-3.4421</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3642</v>
+        <v>1.3334</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3071</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6884</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2091</v>
+        <v>0.0973</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4793</v>
+        <v>0.4485</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.9668</v>
+        <v>12.3092</v>
       </c>
       <c r="E13" t="n">
-        <v>1.943400000000001</v>
+        <v>2.285900000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>10.0231</v>
+        <v>10.0233</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2276000000000011</v>
+        <v>-0.2276000000000002</v>
       </c>
       <c r="H13" t="n">
         <v>-1.1718</v>
@@ -1441,16 +1441,16 @@
         <v>0.9444000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>6.567299999999999</v>
+        <v>6.567299999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>4.578900000000001</v>
+        <v>4.578899999999999</v>
       </c>
       <c r="L13" t="n">
         <v>1.9884</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.795</v>
+        <v>-6.794999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-5.750799999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-1.044</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.087699999999999</v>
+        <v>-1.0877</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.0502</v>
@@ -1468,13 +1468,13 @@
         <v>11.9626</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6325</v>
+        <v>4.975099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8291999999999997</v>
+        <v>-0.4867000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>5.4617</v>
+        <v>5.461600000000001</v>
       </c>
       <c r="V13" t="n">
         <v>8.6495</v>
@@ -1483,7 +1483,7 @@
         <v>9.255699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6063999999999999</v>
+        <v>-0.6064000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7461</v>
+        <v>2.5194</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0136</v>
+        <v>2.2371</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2675</v>
+        <v>0.2823</v>
       </c>
       <c r="G14" t="n">
         <v>2.7974</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1388</v>
+        <v>-0.3656</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.6994</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.216</v>
+        <v>0.3338</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5649999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1749</v>
+        <v>1.1594</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.301</v>
+        <v>-0.2376</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4759</v>
+        <v>1.397</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8098</v>
+        <v>0.3297</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8879</v>
+        <v>-1.0735</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0781</v>
+        <v>1.4033</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8394</v>
+        <v>0.8423</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8577</v>
+        <v>-0.5562</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0183</v>
+        <v>1.3985</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0296</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0302</v>
+        <v>-0.5173</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0598</v>
+        <v>0.0047</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2673</v>
+        <v>-0.8229</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1404</v>
+        <v>-1.1224</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8731</v>
+        <v>0.2995</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2012</v>
+        <v>1.0041</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4611</v>
+        <v>-0.1892</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6624</v>
+        <v>1.1934</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3297</v>
+        <v>0.8098</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0735</v>
+        <v>0.8879</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4033</v>
+        <v>-0.0781</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8423</v>
+        <v>0.8394</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5562</v>
+        <v>0.8577</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3985</v>
+        <v>-0.0183</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.0296</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5173</v>
+        <v>0.0302</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0047</v>
+        <v>-0.0598</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.781</v>
+        <v>-0.438</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3459</v>
+        <v>-1.0286</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4351</v>
+        <v>0.5906</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8843</v>
+        <v>-0.5083</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6984</v>
+        <v>0.8833</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8141</v>
+        <v>-1.3916</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4513</v>
+        <v>0.3872</v>
       </c>
       <c r="H17" t="n">
-        <v>0.113</v>
+        <v>-0.5172</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5642</v>
+        <v>0.9044</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3595</v>
+        <v>1.4265</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7609</v>
+        <v>0.1642</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.1204</v>
+        <v>1.2622</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0917</v>
+        <v>-1.0392</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6479</v>
+        <v>-0.6814</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5562</v>
+        <v>-0.3578</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3272</v>
+        <v>-0.5056</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7487</v>
+        <v>-0.5432</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4214</v>
+        <v>0.0375</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>-1.695</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1608</v>
+        <v>-0.8692</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1377</v>
+        <v>-1.0259</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0232</v>
+        <v>0.1566</v>
       </c>
       <c r="G18" t="n">
         <v>1.4796</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0309</v>
+        <v>-0.7393</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1404</v>
+        <v>-1.0286</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1095</v>
+        <v>0.2893</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7395</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3316</v>
+        <v>-1.2761</v>
       </c>
       <c r="E19" t="n">
-        <v>0.548</v>
+        <v>-2.4807</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8797</v>
+        <v>1.2046</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3872</v>
+        <v>-1.4513</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5172</v>
+        <v>0.113</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9044</v>
+        <v>-1.5642</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4265</v>
+        <v>-1.3595</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1642</v>
+        <v>0.7609</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2622</v>
+        <v>-2.1204</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0392</v>
+        <v>-0.0917</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6814</v>
+        <v>-0.6479</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3578</v>
+        <v>0.5562</v>
       </c>
       <c r="P19" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.329</v>
+        <v>-0.0646</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8784</v>
+        <v>-0.0336</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4505</v>
+        <v>-0.031</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.695</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5374</v>
+        <v>-1.3576</v>
       </c>
       <c r="E20" t="n">
         <v>-0.2518</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2856</v>
+        <v>-1.1058</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6487000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5635</v>
+        <v>-0.3836</v>
       </c>
       <c r="T20" t="n">
         <v>-0.137</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4265</v>
+        <v>-0.2466</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7602</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9162</v>
+        <v>-2.1012</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9693000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9469</v>
+        <v>-1.1319</v>
       </c>
       <c r="G22" t="n">
         <v>-1.086</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1353</v>
+        <v>-0.3203</v>
       </c>
       <c r="T22" t="n">
         <v>-0.548</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4127</v>
+        <v>0.2277</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3727</v>
+        <v>-7.1612</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.8271</v>
+        <v>-7.0506</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4544</v>
+        <v>-0.1106</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4429</v>
@@ -2248,13 +2248,13 @@
         <v>2.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>1.137</v>
+        <v>0.3485</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2463</v>
+        <v>-0.4698</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3834</v>
+        <v>0.8183</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8042</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.9668</v>
+        <v>-10.4767</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.0233</v>
+        <v>-10.0232</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9436</v>
+        <v>-0.4535</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2273000000000001</v>
+        <v>0.2272999999999996</v>
       </c>
       <c r="H24" t="n">
-        <v>1.172000000000001</v>
+        <v>1.172</v>
       </c>
       <c r="I24" t="n">
         <v>-0.9443000000000004</v>
@@ -2311,13 +2311,13 @@
         <v>-6.567299999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.578799999999999</v>
+        <v>-4.5788</v>
       </c>
       <c r="O24" t="n">
         <v>-1.9884</v>
       </c>
       <c r="P24" t="n">
-        <v>1.0875</v>
+        <v>1.087499999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-11.9628</v>
@@ -2326,13 +2326,13 @@
         <v>13.0504</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.6326</v>
+        <v>-3.1424</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.4616</v>
+        <v>-5.461600000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8291999999999999</v>
+        <v>2.3191</v>
       </c>
       <c r="V24" t="n">
         <v>-8.6493</v>
@@ -2341,7 +2341,7 @@
         <v>0.6063999999999998</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.255700000000001</v>
+        <v>-9.255699999999999</v>
       </c>
     </row>
   </sheetData>
